--- a/Resources/Data Structures & Algorithms.xlsx
+++ b/Resources/Data Structures & Algorithms.xlsx
@@ -1161,7 +1161,7 @@
     <t>Painter's Partition Problem</t>
   </si>
   <si>
-    <t>Painter's Partition Problem - Naukri</t>
+    <t>The Painter's Partition Problem-II | Practice | GeeksforGeeks</t>
   </si>
   <si>
     <t>Use binary search on the answer (time). Low = max board length, High = sum of all boards. For a mid time, greedily assign boards to painters and count how many needed. If painters ≤ k → try smaller time, else increase time.</t>

--- a/Resources/Data Structures & Algorithms.xlsx
+++ b/Resources/Data Structures & Algorithms.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="827">
   <si>
     <t>Video Solution</t>
   </si>
@@ -1743,6 +1743,562 @@
   </si>
   <si>
     <t>Create a dummy node pointing to head to handle edge cases (like deleting the head). Move fast pointer n + 1 steps ahead to create a gap of n. Move both fast and slow together until fast reaches NULL. slow will be just before the target node → skip it (slow-&gt;next = slow-&gt;next-&gt;next).</t>
+  </si>
+  <si>
+    <t>L16. Delete the middle node of the LinkedList</t>
+  </si>
+  <si>
+    <t>2095. Delete the Middle Node of a Linked List</t>
+  </si>
+  <si>
+    <t>Delete the Middle Node of a Linked List - LeetCode</t>
+  </si>
+  <si>
+    <t>Use fast, slow and prev pointer to iterate the list, once fast reaches the end, slow is at the middle node and prev is just before slow. Update Pointers and delete the slow node.</t>
+  </si>
+  <si>
+    <t>L26. Sort a Linked List | Merge Sort and Brute Force</t>
+  </si>
+  <si>
+    <t>148. Sort List</t>
+  </si>
+  <si>
+    <t>Sort List - LeetCode</t>
+  </si>
+  <si>
+    <t>The list is split into two halves using slow/fast pointers, where slow stops just before the middle, allowing clean separation. Each half is recursively sorted until single-node lists remain (base case). The two sorted halves are merged in sorted order using the merge() function.</t>
+  </si>
+  <si>
+    <t>L7. Sort a LinkedList of 0's, 1's and 2's | Multiple Approaches</t>
+  </si>
+  <si>
+    <t>Sort a linked list of 0s, 1s and 2s</t>
+  </si>
+  <si>
+    <t>Sort a linked list of 0s, 1s and 2s | Practice | GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>Create three dummy lists (0s, 1s, 2s) and use tail pointers to build them while traversing the original list once. For each node, attach it to the corresponding list based on its value. Connect the three lists in order: 0-list → 1-list → 2-list. Terminate the final tail with NULL and return the head of the 0-list.</t>
+  </si>
+  <si>
+    <t>L12. Find the intersection point of Y LinkedList</t>
+  </si>
+  <si>
+    <t>160. Intersection of Two Linked Lists</t>
+  </si>
+  <si>
+    <t>Intersection of Two Linked Lists - LeetCode</t>
+  </si>
+  <si>
+    <t>Use two pointers starting at headA and headB. When a pointer reaches the end of its list, redirect it to the other list’s head. This makes both pointers traverse lengthA + lengthB, cancelling the length difference. They either meet at the intersection node or both become null (no intersection).</t>
+  </si>
+  <si>
+    <t>L11. Add 1 to a number represented by LinkedList</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add 1 to a Linked List Number
+</t>
+  </si>
+  <si>
+    <t>Add 1 to a Linked List Number | Practice | GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>addOneUntil() uses recursion to go to the last node first, then adds 1 and propagates the carry backward. Each node updates its value as sum % 10 and returns the carry sum / 10. If a carry remains after processing the head (like 999 → 1000), a new node is added at the front.</t>
+  </si>
+  <si>
+    <t>Add Two Numbers Given as LinkedLists | Amazon | Microsoft | Facebook | Qualcomm</t>
+  </si>
+  <si>
+    <t>2. Add Two Numbers</t>
+  </si>
+  <si>
+    <t>Add Two Numbers - LeetCode</t>
+  </si>
+  <si>
+    <t>Just keep adding the numbers from first node and moving the carry forward if generated.</t>
+  </si>
+  <si>
+    <t>L18. Delete all occurrences of a Key in DLL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete all occurrences of a given key in a doubly linked list
+</t>
+  </si>
+  <si>
+    <t>Delete all occurrences of a given key in a doubly linked list | Practice | GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>Traverse the list with a current pointer. When a node matches x, bypass it by linking its prev-&gt;next to current-&gt;next and current-&gt;next-&gt;prev to current-&gt;prev (with null checks for head/tail edge cases). Store the node in toDelete, advance current first, then delete toDelete to avoid a dangling pointer. Non-matching nodes just advance current normally.</t>
+  </si>
+  <si>
+    <t>L19. Find all Pairs with given Sum in DLL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pair Sum in Doubly Linked List
+</t>
+  </si>
+  <si>
+    <t>Pair Sum in Doubly Linked List | Practice | GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>Take 2 pointers, one at the start of the list and one at the end of the list, now close them in together on the basis of sum of the elements at the pointers location</t>
+  </si>
+  <si>
+    <t>L20. Remove duplicates from sorted DLL</t>
+  </si>
+  <si>
+    <t>Remove duplicates from a sorted doubly linked list</t>
+  </si>
+  <si>
+    <t>Remove duplicates from a sorted doubly linked list | Practice | GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>Traverse the list with current. Whenever current-&gt;next has the same value, store it in toDelete, bypass it (current-&gt;next = toDelete-&gt;next), fix the back-link (toDelete-&gt;next-&gt;prev = current), and delete it — without moving current forward, so runs of 3+ duplicates are handled in the same spot. If no duplicate, just advance current.</t>
+  </si>
+  <si>
+    <t>L21. Reverse Nodes in K Group Size of LinkedList</t>
+  </si>
+  <si>
+    <t>25. Reverse Nodes in k-Group</t>
+  </si>
+  <si>
+    <t>Reverse Nodes in k-Group - LeetCode</t>
+  </si>
+  <si>
+    <t>A dummy node is used to simplify edge cases (especially when the head changes after reversal). For each iteration, find the k-th node from groupPrev to check if a full group of k exists. If yes, reverse the next k nodes using standard pointer reversal logic. Reconnect the reversed group back to the previous part of the list. Move groupPrev forward to the end of the reversed group and repeat.</t>
+  </si>
+  <si>
+    <t>L22. Rotate a LinkedList</t>
+  </si>
+  <si>
+    <t>61. Rotate List</t>
+  </si>
+  <si>
+    <t>Rotate List - LeetCode</t>
+  </si>
+  <si>
+    <t>Traverse once to get length and reach the tail, then connect tail → head (make it circular). Reduce rotations using k = k % length. Move length - k - 1 steps from head to find the new tail. New head is newTail-&gt;next; break the circle and return it.</t>
+  </si>
+  <si>
+    <t>L24. Flattening a LinkedList | Multiple Approaches with Dry Run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flattening a Linked List
+</t>
+  </si>
+  <si>
+    <t>Flattening a Linked List | Practice | GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>Each node’s bottom list is already sorted, and the next pointer links multiple such lists. The algorithm recursively flattens the list from right to left: first flatten head-&gt;next, then merge it with head. Merging is done like merge-sort on two sorted linked lists, but using the bottom pointer instead of next. During merge, all next pointers are set to NULL to avoid cycles and keep only a single vertical list. After all recursive merges, the structure becomes one sorted list connected only by bottom pointers.</t>
+  </si>
+  <si>
+    <t>L27. Clone a LinkedList with Next and Random Pointers | Copy List with Random Pointers</t>
+  </si>
+  <si>
+    <t>138. Copy List with Random Pointer</t>
+  </si>
+  <si>
+    <t>Copy List with Random Pointer - LeetCode</t>
+  </si>
+  <si>
+    <t>Insert copies in between original nodes (A → A' → B → B'). Connect random pointers using copy-&gt;random = original-&gt;random-&gt;next, since each copy is right after its original. Separate the two lists, restoring the original and extracting the copied list.</t>
+  </si>
+  <si>
+    <t>8. String to Integer (atoi) (Leetcode Easy)</t>
+  </si>
+  <si>
+    <t>Recursion</t>
+  </si>
+  <si>
+    <t>myAtoi first skips leading spaces, then detects the sign (+ or -), and calls the recursive function. iterate reads digits one-by-one recursively and builds the number using num = num * 10 + digit. Before going deeper, it checks overflow; if the value exceeds INT_MAX or INT_MIN, it immediately returns the clamped limit. Recursion stops when a non-digit or end is reached, and returns the final result as sign * num.</t>
+  </si>
+  <si>
+    <t>POW(x,n) | Binary Exponentiation | Leetcode</t>
+  </si>
+  <si>
+    <t>50. Pow(x, n)</t>
+  </si>
+  <si>
+    <t>Pow(x, n) - LeetCode</t>
+  </si>
+  <si>
+    <t>Instead of multiplying (x) by itself (n) times, repeatedly square the base and halve the exponent. If the exponent is even: (x^n = (x^2)^{n/2}). If odd: (x^n = x \cdot x^{n-1}). This reduces the number of multiplications from O(n) to O(log n) because the exponent shrinks by half each step. For negative exponents, compute the positive power and take the reciprocal: (x^{-n} = 1 / x^n).</t>
+  </si>
+  <si>
+    <t>Count Good Numbers - Leetcode 1922 - Python</t>
+  </si>
+  <si>
+    <t>1922. Count Good Numbers</t>
+  </si>
+  <si>
+    <t>Count Good Numbers - LeetCode</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Recursive Brute Force (Explore all valid strings): </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Build the string one position at a time, trying every valid digit allowed at that position (even digits for even indices, prime digits for odd indices). For each choice, recursively fill the next position until the string reaches length n. Every complete valid string contributes 1 to the total count. This works by enumerating all possibilities, but is slow because the number of combinations grows exponentially. </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Mathematical counting + Fast exponentiation (Count choices per slot): </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Instead of generating strings, count how many independent choices exist for each type of position. Even positions each have 5 choices and odd positions each have 4 choices, so multiply these powers together. Use fast exponentiation to compute large powers efficiently by repeatedly squaring instead of multiplying one-by-one. This avoids enumeration and directly computes the result in logarithmic time.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sort a Stack using recursion | Stacks | Love Babbar DSA Sheet | Amazon🔥</t>
+  </si>
+  <si>
+    <t>Sort a stack</t>
+  </si>
+  <si>
+    <t>Sort a stack | Practice | GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>sortStack() uses recursion to remove all elements one by one, until stack becomes empty. While returning from recursion, it inserts each element back in sorted order using insertInSorted(). insertInSorted() pops elements until it finds the correct position for temp, inserts it, then pushes back the popped elements.</t>
+  </si>
+  <si>
+    <t>Reverse a stack using recursion | Stacks | Love Babbar DSA Sheet | Amazon🔥</t>
+  </si>
+  <si>
+    <t>Reverse a Stack</t>
+  </si>
+  <si>
+    <t>Reverse a Stack | Practice | GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>reverseStack() removes the top element and recursively reverses the remaining stack. After the smaller stack is reversed, insertInReverse() inserts the removed element at the bottom. insertInReverse() works by popping everything until the stack is empty, pushing the element, then restoring all popped elements.</t>
+  </si>
+  <si>
+    <t>POTD- 13/12/2023 | Consecutive 1's not allowed | Problem of the Day | GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>Consecutive 1's not allowed</t>
+  </si>
+  <si>
+    <t>Consecutive 1's not allowed | Practice | GeeksforGeeks</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Recursive Approach (Top-Down Thinking):</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> Define state as: digit (previous bit placed) and length remaining. If previous bit was 0, you can place 0 or 1. If previous bit was 1, you can only place 0 (to avoid consecutive 1s). Recursively explore all valid choices until length becomes 0 (base case). </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Dynamic Programming Approach (Bottom-Up Thinking):</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> endsWithZero = valid strings ending in 0, endsWithOne = valid strings ending in 1. New strings ending in 0 = previous (0 + 1), New strings ending in 1 = previous 0 only. Final answer = endsWithZero + endsWithOne</t>
+    </r>
+  </si>
+  <si>
+    <t>Generate Parentheses - Stack - Leetcode 22</t>
+  </si>
+  <si>
+    <t>22. Generate Parentheses</t>
+  </si>
+  <si>
+    <t>Generate Parentheses - LeetCode</t>
+  </si>
+  <si>
+    <t>Build the parentheses string incrementally while keeping the prefix valid. You may add an opening bracket if you still have openings remaining. You may add a closing bracket only if there are more opens than closes so far (to maintain balance). When the string length reaches 2 × n, record it as a valid solution.</t>
+  </si>
+  <si>
+    <t>Power Set | Print all Subsequences</t>
+  </si>
+  <si>
+    <t>Power Set</t>
+  </si>
+  <si>
+    <t>Power Set | Practice | GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>At each character we have two choices → skip it or include it in the current subsequence. Recursively move to the next index for both choices. When we reach the end of the string, the built string (current) is a valid subsequence. If it is not empty, store it in the result.</t>
+  </si>
+  <si>
+    <t>DP 17. Counts Subsets with Sum K | Dp on Subsequences - YouTube</t>
+  </si>
+  <si>
+    <t>Count all subsequences with sum K</t>
+  </si>
+  <si>
+    <t>Check if there exists a subsequence with sum K | Practice | GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>At each index, you have two choices: include the current element in the subsequence or skip it. If you include it, reduce the remaining sum (sum - arr[index]) and move to the next index. If the sum becomes 0, a valid subsequence is found → return 1. If you reach the end of the array or the sum becomes negative, that path fails → return 0.</t>
+  </si>
+  <si>
+    <t>Check if there exists a subsequence with sum K</t>
+  </si>
+  <si>
+    <t>At each index, you have two choices: include the current element in the subsequence or skip it. If you include it, reduce the remaining sum (sum - arr[index]) and move to the next index. If the sum becomes 0, a valid subsequence is found → return true. If you reach the end of the array or the sum becomes negative, that path fails → return false.</t>
+  </si>
+  <si>
+    <t>L8. Combination Sum | Recursion | Leetcode | C++ | Java</t>
+  </si>
+  <si>
+    <t>39. Combination Sum</t>
+  </si>
+  <si>
+    <t>Combination Sum - LeetCode</t>
+  </si>
+  <si>
+    <t>At each index, we have two choices: pick the element or skip it. If the element is ≤ target, we pick it, reduce the target, and stay at the same index (because elements can be reused). After exploring the pick branch, we backtrack (pop) and explore the skip branch by moving to the next index. When we reach the end of the array and target becomes 0, the current combination is stored in the result.</t>
+  </si>
+  <si>
+    <t>L9. Combination Sum II | Leetcode | Recursion | Java | C++</t>
+  </si>
+  <si>
+    <t>40. Combination Sum II</t>
+  </si>
+  <si>
+    <t>Combination Sum II - LeetCode</t>
+  </si>
+  <si>
+    <t>Sort the array so duplicates are adjacent. At each level, the loop decides which value to start from — advancing i is the implicit skip. Picking candidates[i] and recursing with i+1 explores the entire subtree for that choice, then undoing it moves to the next. If the same value appears twice at the same level, skip it with continue to avoid identical combinations.</t>
+  </si>
+  <si>
+    <t>L10. Subset Sum I | Recursion | C++ | Java</t>
+  </si>
+  <si>
+    <t>Subset Sums</t>
+  </si>
+  <si>
+    <t>Subset Sums | Practice | GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>At each index, you make a binary choice — pick the element (add it to sum) or skip it — then recurse forward. When you hit the end of the array, you've committed to one complete subset, so you record that sum. Since every element independently branches into 2 choices, you generate all 2ⁿ possible subset sums, then sort them.</t>
+  </si>
+  <si>
+    <t>L11. Subset Sum II | Leetcode | Recursion</t>
+  </si>
+  <si>
+    <t>90. Subsets II</t>
+  </si>
+  <si>
+    <t>Subsets II - LeetCode</t>
+  </si>
+  <si>
+    <t>Sort the array first, then use backtracking to build every possible subset. At each recursive call, snapshot the current subset into results before exploring further elements. The key dedup trick: skip an element if it's the same as the previous one at the same recursion depth (i &gt; index &amp;&amp; nums[i] == nums[i-1]).</t>
+  </si>
+  <si>
+    <t>Daily Leetcode #770: May 10, 2022 - 216. Combination Sum III</t>
+  </si>
+  <si>
+    <t>216. Combination Sum III</t>
+  </si>
+  <si>
+    <t>Combination Sum III - LeetCode</t>
+  </si>
+  <si>
+    <t>Start with remaining sum = n, try digits 1→9 in order. At each step, pick digit i, subtract it from sum, and recurse with i+1 (no repeats). If sum == 0 and you have exactly k numbers → valid combination, save it. If sum goes negative or you exceed k numbers → dead end, stop early.</t>
+  </si>
+  <si>
+    <t>Letter Combinations of a Phone Number - Backtracking - Leetcode 17</t>
+  </si>
+  <si>
+    <t>17. Letter Combinations of a Phone Number</t>
+  </si>
+  <si>
+    <t>Letter Combinations of a Phone Number - LeetCode</t>
+  </si>
+  <si>
+    <t>For each digit, you branch into all its possible letters, recursively doing the same for the next digit. Once you've picked one letter per digit, that combination is complete and saved. It's like building a tree where each level is a digit and each node branches into that digit's letters — you collect every root-to-leaf path.</t>
+  </si>
+  <si>
+    <t>DP 53. Palindrome Partitioning - II | Front Partition 🔥</t>
+  </si>
+  <si>
+    <t>131. Palindrome Partitioning</t>
+  </si>
+  <si>
+    <t>Palindrome Partitioning - LeetCode</t>
+  </si>
+  <si>
+    <t>We try every possible first chunk starting at index — if s[index..i] is a palindrome, we take it, add it to our partition, and recurse on the rest starting at i+1. If we reach the end of the string (index == s.size()), it means every chunk we picked was a palindrome — so we save that partition as a valid result. After each recursive call we pop the last chunk (backtrack), so we can try the next possible chunk cleanly without leftover state.</t>
+  </si>
+  <si>
+    <t>Word Search - Backtracking - Leetcode 79 - Python</t>
+  </si>
+  <si>
+    <t>79. Word Search</t>
+  </si>
+  <si>
+    <t>Word Search - LeetCode</t>
+  </si>
+  <si>
+    <t>Start from every cell in the grid. If the cell matches word[index], mark it as visited ('#'), then recursively explore all 4 neighbors for the next character. If any path spells the full word, return true. After exploring, restore the cell so other paths can reuse it. Base case: if index == word.size(), the word is fully matched.</t>
+  </si>
+  <si>
+    <t>L14. N-Queens | Leetcode Hard | Backtracking</t>
+  </si>
+  <si>
+    <t>51. N-Queens</t>
+  </si>
+  <si>
+    <t>N-Queens - LeetCode</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Brute Force: </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Place a queen column by column, and before placing in any row, call isSafe() which manually scans the entire left row + both left diagonals each time.</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> Optimal: </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Replace the isSafe() scan with 3 boolean arrays — leftRow, upperDiagonal, lowerDiagonal — that track occupied rows and diagonals in O(1). The key insight is the diagonal indexing: Lower diagonal → row + col is constant along it → use as index Upper diagonal → row - col is constant along it → shift by n-1 to avoid negatives → n - 1 + col - row. Before placing, check all 3 arrays. Mark on placement, unmark on backtrack.</t>
+    </r>
+  </si>
+  <si>
+    <t>L19. Rat in A Maze | Backtracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rat in a Maze
+</t>
+  </si>
+  <si>
+    <t>Rat in a Maze | Practice | GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>Start at (0,0), and at every cell try all 4 directions (D→L→R→U). Before moving, the bounds/wall/visited check acts as a gate — invalid moves are rejected instantly. When you reach the destination, save the path string. After exploring all directions from a cell, unmark it so other paths can reuse it. Finally, sort the collected paths.</t>
+  </si>
+  <si>
+    <t>Word Break - Dynamic Programming - Leetcode 139 - Python</t>
+  </si>
+  <si>
+    <t>139. Word Break</t>
+  </si>
+  <si>
+    <t>Word Break - LeetCode</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Recursive approach</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">: Try every possible prefix of the string. If the prefix exists in the dictionary, recursively check if the remaining suffix can also be broken. If the suffix reaches empty, the whole string is breakable. </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>DP approach:</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> dp[i] asks — "can the first i characters be broken?" For every position i, look back at all positions j. If dp[j] is true and the window s[j..i] is in the dictionary, mark dp[i] = true. The answer is dp[n].</t>
+    </r>
+  </si>
+  <si>
+    <t>L16. M-Coloring Problem | Backtracking</t>
+  </si>
+  <si>
+    <t>M-Coloring Problem</t>
+  </si>
+  <si>
+    <t>M-Coloring Problem | Practice | GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>Go node by node — for each node, try colors 1 to m. Before assigning, check if any neighbor already holds that color (isSafe). If safe → assign and recurse deeper. If recursion fails or no color works → reset to 0 and backtrack. If all nodes get colored successfully → return true.</t>
+  </si>
+  <si>
+    <t>L15. Sudoko Solver | Backtracking</t>
+  </si>
+  <si>
+    <t>37. Sudoku Solver</t>
+  </si>
+  <si>
+    <t>Sudoku Solver - LeetCode</t>
+  </si>
+  <si>
+    <t>Flatten the 9×9 board into positions 0→80, where row = pos/9 and col = pos%9. For each empty cell ('.'), try digits '1'–'9' and check validity across the row, column, and 3×3 box in a single loop using the trick board[boxRow + i/3][boxCol + i%3]. If a digit is valid, place it and recurse to the next position — if the recursion fails, undo it ('.') and try the next digit. If all 81 positions are filled (pos == 81), return true.</t>
+  </si>
+  <si>
+    <t>EXPRESSION ADD OPERATORS | LEETCODE # 282 | PYTHON SOLUTION</t>
+  </si>
+  <si>
+    <t>282. Expression Add Operators</t>
+  </si>
+  <si>
+    <t>Expression Add Operators - LeetCode</t>
+  </si>
+  <si>
+    <t>DFS over the string — at each index, try consuming 1, 2, 3... digits as the next operand. Skip leading zeros — if the operand starts with '0' and has more than 1 digit, break. First operand has no operator — just seed total and last with it and recurse. + and - are straightforward — update total normally, carry the signed operand as last. * needs the last operand — undo its addition (total - last), then add the multiplied value (last * curr), this handles precedence without any stack</t>
   </si>
   <si>
     <t>L14. Maximum Depth in Binary Tree | Height of Binary Tree | C++ | Java</t>
@@ -2938,7 +3494,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3012,6 +3568,9 @@
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -5467,1106 +6026,1680 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="22"/>
-      <c r="B132" s="20"/>
-      <c r="C132" s="22"/>
-      <c r="D132" s="22"/>
+      <c r="A132" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C132" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="D132" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>503</v>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="22"/>
-      <c r="B133" s="20"/>
-      <c r="C133" s="22"/>
-      <c r="D133" s="22"/>
-      <c r="E133" s="22"/>
+      <c r="A133" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C133" s="14" t="s">
+        <v>505</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="E133" s="13" t="s">
+        <v>507</v>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="22"/>
-      <c r="B134" s="20"/>
-      <c r="C134" s="22"/>
-      <c r="D134" s="22"/>
-      <c r="E134" s="22"/>
+      <c r="A134" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C134" s="14" t="s">
+        <v>509</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="E134" s="13" t="s">
+        <v>511</v>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="22"/>
-      <c r="B135" s="20"/>
-      <c r="C135" s="22"/>
-      <c r="D135" s="22"/>
-      <c r="E135" s="22"/>
+      <c r="A135" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C135" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="E135" s="13" t="s">
+        <v>515</v>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" s="22"/>
-      <c r="B136" s="20"/>
-      <c r="C136" s="22"/>
-      <c r="D136" s="22"/>
-      <c r="E136" s="22"/>
+      <c r="A136" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C136" s="14" t="s">
+        <v>517</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>518</v>
+      </c>
+      <c r="E136" s="13" t="s">
+        <v>519</v>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="22"/>
-      <c r="B137" s="20"/>
-      <c r="C137" s="22"/>
-      <c r="D137" s="22"/>
-      <c r="E137" s="22"/>
+      <c r="A137" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C137" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="E137" s="13" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C141" s="17" t="s">
+        <v>537</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="E145" s="7" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C155" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C160" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C161" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C163" s="17" t="s">
+        <v>622</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="E164" s="7" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C165" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="E165" s="7" t="s">
+        <v>632</v>
+      </c>
     </row>
     <row r="166">
-      <c r="A166" s="10" t="s">
-        <v>500</v>
+      <c r="A166" s="9" t="s">
+        <v>633</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C166" s="15" t="s">
-        <v>502</v>
-      </c>
-      <c r="D166" s="12" t="s">
-        <v>503</v>
-      </c>
-      <c r="E166" s="13" t="s">
-        <v>504</v>
+        <v>553</v>
+      </c>
+      <c r="C166" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="10" t="s">
-        <v>505</v>
+      <c r="A167" s="3" t="s">
+        <v>637</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C167" s="11" t="s">
-        <v>506</v>
-      </c>
-      <c r="D167" s="12" t="s">
-        <v>507</v>
-      </c>
-      <c r="E167" s="13" t="s">
-        <v>508</v>
+        <v>553</v>
+      </c>
+      <c r="C167" s="17" t="s">
+        <v>638</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="10" t="s">
-        <v>509</v>
+      <c r="A168" s="9" t="s">
+        <v>641</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C168" s="11" t="s">
-        <v>510</v>
-      </c>
-      <c r="D168" s="12" t="s">
-        <v>511</v>
-      </c>
-      <c r="E168" s="13" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="16" t="s">
-        <v>513</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C169" s="19" t="s">
-        <v>514</v>
-      </c>
-      <c r="D169" s="12" t="s">
-        <v>515</v>
-      </c>
-      <c r="E169" s="13" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="16" t="s">
-        <v>516</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C170" s="11" t="s">
-        <v>517</v>
-      </c>
-      <c r="D170" s="12" t="s">
-        <v>518</v>
-      </c>
-      <c r="E170" s="13" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="10" t="s">
-        <v>520</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C171" s="14" t="s">
-        <v>521</v>
-      </c>
-      <c r="D171" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="E171" s="13" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="16" t="s">
-        <v>523</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C172" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="D172" s="12" t="s">
-        <v>525</v>
-      </c>
-      <c r="E172" s="13" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="10" t="s">
-        <v>526</v>
-      </c>
-      <c r="B173" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C173" s="19" t="s">
-        <v>527</v>
-      </c>
-      <c r="D173" s="12" t="s">
-        <v>528</v>
-      </c>
-      <c r="E173" s="13" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="16" t="s">
-        <v>530</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C174" s="14" t="s">
-        <v>531</v>
-      </c>
-      <c r="D174" s="12" t="s">
-        <v>532</v>
-      </c>
-      <c r="E174" s="13" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="10" t="s">
-        <v>534</v>
-      </c>
-      <c r="B175" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C175" s="23" t="s">
-        <v>535</v>
-      </c>
-      <c r="D175" s="12" t="s">
-        <v>536</v>
-      </c>
-      <c r="E175" s="13" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="10" t="s">
-        <v>538</v>
-      </c>
-      <c r="B176" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C176" s="23" t="s">
-        <v>539</v>
-      </c>
-      <c r="D176" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="E176" s="13" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="10" t="s">
-        <v>542</v>
-      </c>
-      <c r="B177" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C177" s="11" t="s">
-        <v>543</v>
-      </c>
-      <c r="D177" s="12" t="s">
-        <v>544</v>
-      </c>
-      <c r="E177" s="13" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="10" t="s">
-        <v>546</v>
-      </c>
-      <c r="B178" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C178" s="14" t="s">
-        <v>547</v>
-      </c>
-      <c r="D178" s="12" t="s">
-        <v>548</v>
-      </c>
-      <c r="E178" s="13" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="10" t="s">
-        <v>550</v>
-      </c>
-      <c r="B179" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C179" s="14" t="s">
-        <v>551</v>
-      </c>
-      <c r="D179" s="12" t="s">
-        <v>552</v>
-      </c>
-      <c r="E179" s="13" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="10" t="s">
-        <v>554</v>
-      </c>
-      <c r="B180" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C180" s="14" t="s">
-        <v>555</v>
-      </c>
-      <c r="D180" s="12" t="s">
-        <v>556</v>
-      </c>
-      <c r="E180" s="13" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="16" t="s">
-        <v>558</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C181" s="14" t="s">
-        <v>559</v>
-      </c>
-      <c r="D181" s="12" t="s">
-        <v>560</v>
-      </c>
-      <c r="E181" s="13" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="10" t="s">
-        <v>558</v>
-      </c>
-      <c r="B182" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C182" s="24" t="s">
-        <v>562</v>
-      </c>
-      <c r="D182" s="12" t="s">
-        <v>563</v>
-      </c>
-      <c r="E182" s="13" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="10" t="s">
-        <v>565</v>
-      </c>
-      <c r="B183" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C183" s="14" t="s">
-        <v>566</v>
-      </c>
-      <c r="D183" s="12" t="s">
-        <v>567</v>
-      </c>
-      <c r="E183" s="13" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="10" t="s">
-        <v>569</v>
-      </c>
-      <c r="B184" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C184" s="19" t="s">
-        <v>570</v>
-      </c>
-      <c r="D184" s="12" t="s">
-        <v>571</v>
-      </c>
-      <c r="E184" s="13" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="10" t="s">
-        <v>573</v>
-      </c>
-      <c r="B185" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C185" s="11" t="s">
-        <v>574</v>
-      </c>
-      <c r="D185" s="12" t="s">
-        <v>575</v>
-      </c>
-      <c r="E185" s="13" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="16" t="s">
-        <v>577</v>
-      </c>
-      <c r="B186" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C186" s="11" t="s">
-        <v>578</v>
-      </c>
-      <c r="D186" s="12" t="s">
-        <v>579</v>
-      </c>
-      <c r="E186" s="13" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="10" t="s">
-        <v>581</v>
-      </c>
-      <c r="B187" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C187" s="14" t="s">
-        <v>582</v>
-      </c>
-      <c r="D187" s="12" t="s">
-        <v>583</v>
-      </c>
-      <c r="E187" s="13" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="10" t="s">
-        <v>585</v>
-      </c>
-      <c r="B188" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C188" s="14" t="s">
-        <v>586</v>
-      </c>
-      <c r="D188" s="12" t="s">
-        <v>587</v>
-      </c>
-      <c r="E188" s="13" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="10" t="s">
-        <v>589</v>
-      </c>
-      <c r="B189" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C189" s="19" t="s">
-        <v>590</v>
-      </c>
-      <c r="D189" s="12" t="s">
-        <v>591</v>
-      </c>
-      <c r="E189" s="13" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="10" t="s">
-        <v>593</v>
-      </c>
-      <c r="B190" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C190" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="D190" s="12" t="s">
-        <v>595</v>
-      </c>
-      <c r="E190" s="13" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="10" t="s">
-        <v>593</v>
-      </c>
-      <c r="B191" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C191" s="11" t="s">
-        <v>597</v>
-      </c>
-      <c r="D191" s="12" t="s">
-        <v>598</v>
-      </c>
-      <c r="E191" s="13" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="10" t="s">
-        <v>600</v>
-      </c>
-      <c r="B192" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C192" s="14" t="s">
-        <v>601</v>
-      </c>
-      <c r="D192" s="12" t="s">
-        <v>602</v>
-      </c>
-      <c r="E192" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="22"/>
-      <c r="B193" s="20"/>
-      <c r="C193" s="22"/>
-      <c r="D193" s="22"/>
-      <c r="E193" s="22"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="22"/>
-      <c r="B194" s="20"/>
-      <c r="C194" s="22"/>
-      <c r="D194" s="22"/>
-      <c r="E194" s="22"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="22"/>
-      <c r="B195" s="20"/>
-      <c r="C195" s="22"/>
-      <c r="D195" s="22"/>
-      <c r="E195" s="22"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="22"/>
-      <c r="B196" s="20"/>
-      <c r="C196" s="22"/>
-      <c r="D196" s="22"/>
-      <c r="E196" s="22"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="22"/>
-      <c r="B197" s="20"/>
-      <c r="C197" s="22"/>
-      <c r="D197" s="22"/>
-      <c r="E197" s="22"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="22"/>
-      <c r="B198" s="20"/>
-      <c r="C198" s="22"/>
-      <c r="D198" s="22"/>
-      <c r="E198" s="22"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="22"/>
-      <c r="B199" s="20"/>
-      <c r="C199" s="22"/>
-      <c r="D199" s="22"/>
-      <c r="E199" s="22"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="13"/>
-      <c r="B200" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="C200" s="11" t="s">
-        <v>605</v>
-      </c>
-      <c r="D200" s="12" t="s">
-        <v>606</v>
-      </c>
-      <c r="E200" s="13" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="13"/>
-      <c r="B201" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="C201" s="11" t="s">
-        <v>608</v>
-      </c>
-      <c r="D201" s="12" t="s">
-        <v>609</v>
-      </c>
-      <c r="E201" s="13" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="10" t="s">
-        <v>611</v>
-      </c>
-      <c r="B202" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="C202" s="11" t="s">
-        <v>612</v>
-      </c>
-      <c r="D202" s="12" t="s">
-        <v>613</v>
-      </c>
-      <c r="E202" s="13" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="10" t="s">
-        <v>614</v>
-      </c>
-      <c r="B203" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="C203" s="11" t="s">
-        <v>615</v>
-      </c>
-      <c r="D203" s="12" t="s">
-        <v>616</v>
-      </c>
-      <c r="E203" s="13" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="10" t="s">
-        <v>617</v>
-      </c>
-      <c r="B204" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="C204" s="14" t="s">
-        <v>618</v>
-      </c>
-      <c r="D204" s="12" t="s">
-        <v>619</v>
-      </c>
-      <c r="E204" s="13" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="22"/>
-      <c r="B205" s="20"/>
-      <c r="C205" s="22"/>
-      <c r="D205" s="22"/>
-      <c r="E205" s="22"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="22"/>
-      <c r="B206" s="20"/>
-      <c r="C206" s="22"/>
-      <c r="D206" s="22"/>
-      <c r="E206" s="22"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="22"/>
-      <c r="B207" s="20"/>
-      <c r="C207" s="22"/>
-      <c r="D207" s="22"/>
-      <c r="E207" s="22"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="22"/>
-      <c r="B208" s="20"/>
-      <c r="C208" s="22"/>
-      <c r="D208" s="22"/>
-      <c r="E208" s="22"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="22"/>
-      <c r="B209" s="20"/>
-      <c r="C209" s="22"/>
-      <c r="D209" s="22"/>
-      <c r="E209" s="22"/>
+      <c r="C168" s="17" t="s">
+        <v>642</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>644</v>
+      </c>
     </row>
     <row r="210">
-      <c r="A210" s="22"/>
-      <c r="B210" s="20"/>
-      <c r="C210" s="22"/>
-      <c r="D210" s="22"/>
-      <c r="E210" s="22"/>
+      <c r="A210" s="10" t="s">
+        <v>645</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C210" s="15" t="s">
+        <v>647</v>
+      </c>
+      <c r="D210" s="12" t="s">
+        <v>648</v>
+      </c>
+      <c r="E210" s="13" t="s">
+        <v>649</v>
+      </c>
     </row>
     <row r="211">
-      <c r="A211" s="22"/>
-      <c r="B211" s="20"/>
-      <c r="C211" s="22"/>
-      <c r="D211" s="22"/>
-      <c r="E211" s="22"/>
+      <c r="A211" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C211" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="D211" s="12" t="s">
+        <v>652</v>
+      </c>
+      <c r="E211" s="13" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="212">
-      <c r="A212" s="22"/>
-      <c r="B212" s="20"/>
-      <c r="C212" s="22"/>
-      <c r="D212" s="22"/>
-      <c r="E212" s="22"/>
+      <c r="A212" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C212" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="D212" s="12" t="s">
+        <v>656</v>
+      </c>
+      <c r="E212" s="13" t="s">
+        <v>657</v>
+      </c>
     </row>
     <row r="213">
-      <c r="A213" s="22"/>
-      <c r="B213" s="20"/>
-      <c r="C213" s="22"/>
-      <c r="D213" s="22"/>
-      <c r="E213" s="22"/>
+      <c r="A213" s="16" t="s">
+        <v>658</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C213" s="19" t="s">
+        <v>659</v>
+      </c>
+      <c r="D213" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="E213" s="13" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="214">
-      <c r="A214" s="22"/>
-      <c r="B214" s="20"/>
-      <c r="C214" s="22"/>
-      <c r="D214" s="22"/>
-      <c r="E214" s="22"/>
+      <c r="A214" s="16" t="s">
+        <v>661</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C214" s="11" t="s">
+        <v>662</v>
+      </c>
+      <c r="D214" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="E214" s="13" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="215">
-      <c r="A215" s="22"/>
-      <c r="B215" s="20"/>
-      <c r="C215" s="22"/>
-      <c r="D215" s="22"/>
-      <c r="E215" s="22"/>
+      <c r="A215" s="10" t="s">
+        <v>665</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C215" s="14" t="s">
+        <v>666</v>
+      </c>
+      <c r="D215" s="12" t="s">
+        <v>667</v>
+      </c>
+      <c r="E215" s="13" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="216">
-      <c r="A216" s="22"/>
-      <c r="B216" s="20"/>
-      <c r="C216" s="22"/>
-      <c r="D216" s="22"/>
-      <c r="E216" s="22"/>
+      <c r="A216" s="16" t="s">
+        <v>668</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C216" s="14" t="s">
+        <v>669</v>
+      </c>
+      <c r="D216" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="E216" s="13" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="217">
-      <c r="A217" s="22"/>
-      <c r="B217" s="20"/>
-      <c r="C217" s="22"/>
-      <c r="D217" s="22"/>
-      <c r="E217" s="22"/>
+      <c r="A217" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C217" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="D217" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E217" s="13" t="s">
+        <v>674</v>
+      </c>
     </row>
     <row r="218">
-      <c r="A218" s="22"/>
-      <c r="B218" s="20"/>
-      <c r="C218" s="22"/>
-      <c r="D218" s="22"/>
-      <c r="E218" s="22"/>
+      <c r="A218" s="16" t="s">
+        <v>675</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C218" s="14" t="s">
+        <v>676</v>
+      </c>
+      <c r="D218" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="E218" s="13" t="s">
+        <v>678</v>
+      </c>
     </row>
     <row r="219">
-      <c r="A219" s="22"/>
-      <c r="B219" s="20"/>
-      <c r="C219" s="22"/>
-      <c r="D219" s="22"/>
-      <c r="E219" s="22"/>
+      <c r="A219" s="10" t="s">
+        <v>679</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C219" s="23" t="s">
+        <v>680</v>
+      </c>
+      <c r="D219" s="12" t="s">
+        <v>681</v>
+      </c>
+      <c r="E219" s="13" t="s">
+        <v>682</v>
+      </c>
     </row>
     <row r="220">
-      <c r="A220" s="22"/>
-      <c r="B220" s="20"/>
-      <c r="C220" s="22"/>
-      <c r="D220" s="22"/>
-      <c r="E220" s="22"/>
+      <c r="A220" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C220" s="23" t="s">
+        <v>684</v>
+      </c>
+      <c r="D220" s="12" t="s">
+        <v>685</v>
+      </c>
+      <c r="E220" s="13" t="s">
+        <v>686</v>
+      </c>
     </row>
     <row r="221">
-      <c r="A221" s="22"/>
-      <c r="B221" s="20"/>
-      <c r="C221" s="22"/>
-      <c r="D221" s="22"/>
-      <c r="E221" s="22"/>
+      <c r="A221" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C221" s="11" t="s">
+        <v>688</v>
+      </c>
+      <c r="D221" s="12" t="s">
+        <v>689</v>
+      </c>
+      <c r="E221" s="13" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="222">
-      <c r="A222" s="22"/>
-      <c r="B222" s="20"/>
-      <c r="C222" s="22"/>
-      <c r="D222" s="22"/>
-      <c r="E222" s="22"/>
+      <c r="A222" s="10" t="s">
+        <v>691</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C222" s="14" t="s">
+        <v>692</v>
+      </c>
+      <c r="D222" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="E222" s="13" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="223">
-      <c r="A223" s="22"/>
-      <c r="B223" s="20"/>
-      <c r="C223" s="22"/>
-      <c r="D223" s="22"/>
-      <c r="E223" s="22"/>
+      <c r="A223" s="10" t="s">
+        <v>695</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C223" s="14" t="s">
+        <v>696</v>
+      </c>
+      <c r="D223" s="12" t="s">
+        <v>697</v>
+      </c>
+      <c r="E223" s="13" t="s">
+        <v>698</v>
+      </c>
     </row>
     <row r="224">
-      <c r="A224" s="22"/>
-      <c r="B224" s="20"/>
-      <c r="C224" s="22"/>
-      <c r="D224" s="22"/>
-      <c r="E224" s="22"/>
+      <c r="A224" s="10" t="s">
+        <v>699</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C224" s="14" t="s">
+        <v>700</v>
+      </c>
+      <c r="D224" s="12" t="s">
+        <v>701</v>
+      </c>
+      <c r="E224" s="13" t="s">
+        <v>702</v>
+      </c>
     </row>
     <row r="225">
-      <c r="A225" s="22"/>
-      <c r="B225" s="20"/>
-      <c r="C225" s="22"/>
-      <c r="D225" s="22"/>
-      <c r="E225" s="22"/>
+      <c r="A225" s="16" t="s">
+        <v>703</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C225" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="D225" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="E225" s="13" t="s">
+        <v>706</v>
+      </c>
     </row>
     <row r="226">
-      <c r="A226" s="22"/>
-      <c r="B226" s="20"/>
-      <c r="C226" s="22"/>
-      <c r="D226" s="22"/>
-      <c r="E226" s="22"/>
+      <c r="A226" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C226" s="24" t="s">
+        <v>707</v>
+      </c>
+      <c r="D226" s="12" t="s">
+        <v>708</v>
+      </c>
+      <c r="E226" s="13" t="s">
+        <v>709</v>
+      </c>
     </row>
     <row r="227">
-      <c r="A227" s="22"/>
-      <c r="B227" s="20"/>
-      <c r="C227" s="22"/>
-      <c r="D227" s="22"/>
-      <c r="E227" s="22"/>
+      <c r="A227" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C227" s="14" t="s">
+        <v>711</v>
+      </c>
+      <c r="D227" s="12" t="s">
+        <v>712</v>
+      </c>
+      <c r="E227" s="13" t="s">
+        <v>713</v>
+      </c>
     </row>
     <row r="228">
-      <c r="A228" s="22"/>
-      <c r="B228" s="20"/>
-      <c r="C228" s="22"/>
-      <c r="D228" s="22"/>
-      <c r="E228" s="22"/>
+      <c r="A228" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C228" s="19" t="s">
+        <v>715</v>
+      </c>
+      <c r="D228" s="12" t="s">
+        <v>716</v>
+      </c>
+      <c r="E228" s="13" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="229">
-      <c r="A229" s="22"/>
-      <c r="B229" s="20"/>
-      <c r="C229" s="22"/>
-      <c r="D229" s="22"/>
-      <c r="E229" s="22"/>
+      <c r="A229" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C229" s="11" t="s">
+        <v>719</v>
+      </c>
+      <c r="D229" s="12" t="s">
+        <v>720</v>
+      </c>
+      <c r="E229" s="13" t="s">
+        <v>721</v>
+      </c>
     </row>
     <row r="230">
-      <c r="A230" s="22"/>
-      <c r="B230" s="20"/>
-      <c r="C230" s="22"/>
-      <c r="D230" s="22"/>
-      <c r="E230" s="22"/>
+      <c r="A230" s="16" t="s">
+        <v>722</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C230" s="11" t="s">
+        <v>723</v>
+      </c>
+      <c r="D230" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="E230" s="13" t="s">
+        <v>725</v>
+      </c>
     </row>
     <row r="231">
-      <c r="A231" s="22"/>
-      <c r="B231" s="20"/>
-      <c r="C231" s="22"/>
-      <c r="D231" s="22"/>
-      <c r="E231" s="22"/>
+      <c r="A231" s="10" t="s">
+        <v>726</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C231" s="14" t="s">
+        <v>727</v>
+      </c>
+      <c r="D231" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="E231" s="13" t="s">
+        <v>729</v>
+      </c>
     </row>
     <row r="232">
-      <c r="A232" s="22"/>
-      <c r="B232" s="20"/>
-      <c r="C232" s="22"/>
-      <c r="D232" s="22"/>
-      <c r="E232" s="22"/>
+      <c r="A232" s="10" t="s">
+        <v>730</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C232" s="14" t="s">
+        <v>731</v>
+      </c>
+      <c r="D232" s="12" t="s">
+        <v>732</v>
+      </c>
+      <c r="E232" s="13" t="s">
+        <v>733</v>
+      </c>
     </row>
     <row r="233">
-      <c r="A233" s="22"/>
-      <c r="B233" s="20"/>
-      <c r="C233" s="22"/>
-      <c r="D233" s="22"/>
-      <c r="E233" s="22"/>
+      <c r="A233" s="10" t="s">
+        <v>734</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C233" s="19" t="s">
+        <v>735</v>
+      </c>
+      <c r="D233" s="12" t="s">
+        <v>736</v>
+      </c>
+      <c r="E233" s="13" t="s">
+        <v>737</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="10" t="s">
-        <v>621</v>
+        <v>738</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C234" s="14" t="s">
-        <v>623</v>
+        <v>646</v>
+      </c>
+      <c r="C234" s="11" t="s">
+        <v>739</v>
       </c>
       <c r="D234" s="12" t="s">
-        <v>624</v>
+        <v>740</v>
       </c>
       <c r="E234" s="13" t="s">
-        <v>625</v>
+        <v>741</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="10" t="s">
-        <v>626</v>
+        <v>738</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>622</v>
+        <v>646</v>
       </c>
       <c r="C235" s="11" t="s">
-        <v>627</v>
+        <v>742</v>
       </c>
       <c r="D235" s="12" t="s">
-        <v>628</v>
+        <v>743</v>
       </c>
       <c r="E235" s="13" t="s">
-        <v>629</v>
+        <v>744</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="10" t="s">
-        <v>630</v>
+        <v>745</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C236" s="11" t="s">
-        <v>631</v>
+        <v>646</v>
+      </c>
+      <c r="C236" s="14" t="s">
+        <v>746</v>
       </c>
       <c r="D236" s="12" t="s">
-        <v>632</v>
+        <v>747</v>
       </c>
       <c r="E236" s="13" t="s">
-        <v>633</v>
+        <v>748</v>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="16" t="s">
-        <v>634</v>
-      </c>
-      <c r="B237" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C237" s="14" t="s">
-        <v>635</v>
-      </c>
-      <c r="D237" s="12" t="s">
-        <v>636</v>
-      </c>
-      <c r="E237" s="13" t="s">
-        <v>637</v>
-      </c>
+      <c r="A237" s="22"/>
+      <c r="B237" s="20"/>
+      <c r="C237" s="22"/>
+      <c r="D237" s="25"/>
+      <c r="E237" s="22"/>
     </row>
     <row r="238">
-      <c r="A238" s="10" t="s">
-        <v>638</v>
-      </c>
-      <c r="B238" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C238" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="D238" s="12" t="s">
-        <v>640</v>
-      </c>
-      <c r="E238" s="13" t="s">
-        <v>641</v>
-      </c>
+      <c r="A238" s="22"/>
+      <c r="B238" s="20"/>
+      <c r="C238" s="22"/>
+      <c r="D238" s="22"/>
+      <c r="E238" s="22"/>
     </row>
     <row r="239">
-      <c r="A239" s="16" t="s">
-        <v>642</v>
-      </c>
-      <c r="B239" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C239" s="14" t="s">
-        <v>643</v>
-      </c>
-      <c r="D239" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="E239" s="13" t="s">
-        <v>645</v>
-      </c>
+      <c r="A239" s="22"/>
+      <c r="B239" s="20"/>
+      <c r="C239" s="22"/>
+      <c r="D239" s="22"/>
+      <c r="E239" s="22"/>
     </row>
     <row r="240">
-      <c r="A240" s="16" t="s">
-        <v>646</v>
-      </c>
-      <c r="B240" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C240" s="14" t="s">
-        <v>647</v>
-      </c>
-      <c r="D240" s="12" t="s">
-        <v>648</v>
-      </c>
-      <c r="E240" s="13" t="s">
-        <v>649</v>
-      </c>
+      <c r="A240" s="22"/>
+      <c r="B240" s="20"/>
+      <c r="C240" s="22"/>
+      <c r="D240" s="22"/>
+      <c r="E240" s="22"/>
     </row>
     <row r="241">
-      <c r="A241" s="16" t="s">
-        <v>650</v>
-      </c>
-      <c r="B241" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C241" s="23" t="s">
-        <v>651</v>
-      </c>
-      <c r="D241" s="12" t="s">
-        <v>652</v>
-      </c>
-      <c r="E241" s="13" t="s">
-        <v>653</v>
-      </c>
+      <c r="A241" s="22"/>
+      <c r="B241" s="20"/>
+      <c r="C241" s="22"/>
+      <c r="D241" s="22"/>
+      <c r="E241" s="22"/>
     </row>
     <row r="242">
-      <c r="A242" s="10" t="s">
-        <v>654</v>
-      </c>
-      <c r="B242" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C242" s="14" t="s">
-        <v>655</v>
-      </c>
-      <c r="D242" s="12" t="s">
-        <v>656</v>
-      </c>
-      <c r="E242" s="13" t="s">
-        <v>657</v>
-      </c>
+      <c r="A242" s="22"/>
+      <c r="B242" s="20"/>
+      <c r="C242" s="22"/>
+      <c r="D242" s="22"/>
+      <c r="E242" s="22"/>
     </row>
     <row r="243">
-      <c r="A243" s="10" t="s">
-        <v>658</v>
-      </c>
-      <c r="B243" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C243" s="14" t="s">
-        <v>659</v>
-      </c>
-      <c r="D243" s="12" t="s">
-        <v>660</v>
-      </c>
-      <c r="E243" s="13" t="s">
-        <v>661</v>
-      </c>
+      <c r="A243" s="22"/>
+      <c r="B243" s="20"/>
+      <c r="C243" s="22"/>
+      <c r="D243" s="22"/>
+      <c r="E243" s="22"/>
     </row>
     <row r="244">
-      <c r="A244" s="10" t="s">
-        <v>662</v>
-      </c>
+      <c r="A244" s="13"/>
       <c r="B244" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C244" s="14" t="s">
-        <v>663</v>
+        <v>749</v>
+      </c>
+      <c r="C244" s="11" t="s">
+        <v>750</v>
       </c>
       <c r="D244" s="12" t="s">
-        <v>664</v>
+        <v>751</v>
       </c>
       <c r="E244" s="13" t="s">
-        <v>665</v>
+        <v>752</v>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="10" t="s">
-        <v>666</v>
-      </c>
+      <c r="A245" s="13"/>
       <c r="B245" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C245" s="14" t="s">
-        <v>667</v>
+        <v>749</v>
+      </c>
+      <c r="C245" s="11" t="s">
+        <v>753</v>
       </c>
       <c r="D245" s="12" t="s">
-        <v>668</v>
+        <v>754</v>
       </c>
       <c r="E245" s="13" t="s">
-        <v>669</v>
+        <v>755</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="10" t="s">
-        <v>670</v>
+        <v>756</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C246" s="19" t="s">
-        <v>671</v>
+        <v>749</v>
+      </c>
+      <c r="C246" s="11" t="s">
+        <v>757</v>
       </c>
       <c r="D246" s="12" t="s">
-        <v>672</v>
+        <v>758</v>
       </c>
       <c r="E246" s="13" t="s">
-        <v>673</v>
+        <v>653</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="10" t="s">
-        <v>674</v>
+        <v>759</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C247" s="14" t="s">
-        <v>675</v>
+        <v>749</v>
+      </c>
+      <c r="C247" s="11" t="s">
+        <v>760</v>
       </c>
       <c r="D247" s="12" t="s">
-        <v>676</v>
+        <v>761</v>
       </c>
       <c r="E247" s="13" t="s">
-        <v>677</v>
+        <v>657</v>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="16" t="s">
-        <v>678</v>
+      <c r="A248" s="10" t="s">
+        <v>762</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>622</v>
+        <v>749</v>
       </c>
       <c r="C248" s="14" t="s">
-        <v>679</v>
+        <v>763</v>
       </c>
       <c r="D248" s="12" t="s">
-        <v>680</v>
+        <v>764</v>
       </c>
       <c r="E248" s="13" t="s">
-        <v>681</v>
+        <v>765</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="22"/>
+      <c r="B249" s="20"/>
+      <c r="C249" s="22"/>
+      <c r="D249" s="22"/>
+      <c r="E249" s="22"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="22"/>
+      <c r="B250" s="20"/>
+      <c r="C250" s="22"/>
+      <c r="D250" s="22"/>
+      <c r="E250" s="22"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="22"/>
+      <c r="B251" s="20"/>
+      <c r="C251" s="22"/>
+      <c r="D251" s="22"/>
+      <c r="E251" s="22"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="22"/>
+      <c r="B252" s="20"/>
+      <c r="C252" s="22"/>
+      <c r="D252" s="22"/>
+      <c r="E252" s="22"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="22"/>
+      <c r="B253" s="20"/>
+      <c r="C253" s="22"/>
+      <c r="D253" s="22"/>
+      <c r="E253" s="22"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="22"/>
+      <c r="B254" s="20"/>
+      <c r="C254" s="22"/>
+      <c r="D254" s="22"/>
+      <c r="E254" s="22"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="22"/>
+      <c r="B255" s="20"/>
+      <c r="C255" s="22"/>
+      <c r="D255" s="22"/>
+      <c r="E255" s="22"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="22"/>
+      <c r="B256" s="20"/>
+      <c r="C256" s="22"/>
+      <c r="D256" s="22"/>
+      <c r="E256" s="22"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="22"/>
+      <c r="B257" s="20"/>
+      <c r="C257" s="22"/>
+      <c r="D257" s="22"/>
+      <c r="E257" s="22"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="22"/>
+      <c r="B258" s="20"/>
+      <c r="C258" s="22"/>
+      <c r="D258" s="22"/>
+      <c r="E258" s="22"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="22"/>
+      <c r="B259" s="20"/>
+      <c r="C259" s="22"/>
+      <c r="D259" s="22"/>
+      <c r="E259" s="22"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="22"/>
+      <c r="B260" s="20"/>
+      <c r="C260" s="22"/>
+      <c r="D260" s="22"/>
+      <c r="E260" s="22"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="22"/>
+      <c r="B261" s="20"/>
+      <c r="C261" s="22"/>
+      <c r="D261" s="22"/>
+      <c r="E261" s="22"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="22"/>
+      <c r="B262" s="20"/>
+      <c r="C262" s="22"/>
+      <c r="D262" s="22"/>
+      <c r="E262" s="22"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="22"/>
+      <c r="B263" s="20"/>
+      <c r="C263" s="22"/>
+      <c r="D263" s="22"/>
+      <c r="E263" s="22"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="22"/>
+      <c r="B264" s="20"/>
+      <c r="C264" s="22"/>
+      <c r="D264" s="22"/>
+      <c r="E264" s="22"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="22"/>
+      <c r="B265" s="20"/>
+      <c r="C265" s="22"/>
+      <c r="D265" s="22"/>
+      <c r="E265" s="22"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="22"/>
+      <c r="B266" s="20"/>
+      <c r="C266" s="22"/>
+      <c r="D266" s="22"/>
+      <c r="E266" s="22"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="22"/>
+      <c r="B267" s="20"/>
+      <c r="C267" s="22"/>
+      <c r="D267" s="22"/>
+      <c r="E267" s="22"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="22"/>
+      <c r="B268" s="20"/>
+      <c r="C268" s="22"/>
+      <c r="D268" s="22"/>
+      <c r="E268" s="22"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="22"/>
+      <c r="B269" s="20"/>
+      <c r="C269" s="22"/>
+      <c r="D269" s="22"/>
+      <c r="E269" s="22"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="22"/>
+      <c r="B270" s="20"/>
+      <c r="C270" s="22"/>
+      <c r="D270" s="22"/>
+      <c r="E270" s="22"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="22"/>
+      <c r="B271" s="20"/>
+      <c r="C271" s="22"/>
+      <c r="D271" s="22"/>
+      <c r="E271" s="22"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="22"/>
+      <c r="B272" s="20"/>
+      <c r="C272" s="22"/>
+      <c r="D272" s="22"/>
+      <c r="E272" s="22"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="22"/>
+      <c r="B273" s="20"/>
+      <c r="C273" s="22"/>
+      <c r="D273" s="22"/>
+      <c r="E273" s="22"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="22"/>
+      <c r="B274" s="20"/>
+      <c r="C274" s="22"/>
+      <c r="D274" s="22"/>
+      <c r="E274" s="22"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="22"/>
+      <c r="B275" s="20"/>
+      <c r="C275" s="22"/>
+      <c r="D275" s="22"/>
+      <c r="E275" s="22"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="22"/>
+      <c r="B276" s="20"/>
+      <c r="C276" s="22"/>
+      <c r="D276" s="22"/>
+      <c r="E276" s="22"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="22"/>
+      <c r="B277" s="20"/>
+      <c r="C277" s="22"/>
+      <c r="D277" s="22"/>
+      <c r="E277" s="22"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C278" s="14" t="s">
+        <v>768</v>
+      </c>
+      <c r="D278" s="12" t="s">
+        <v>769</v>
+      </c>
+      <c r="E278" s="13" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C279" s="11" t="s">
+        <v>772</v>
+      </c>
+      <c r="D279" s="12" t="s">
+        <v>773</v>
+      </c>
+      <c r="E279" s="13" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="10" t="s">
+        <v>775</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C280" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="D280" s="12" t="s">
+        <v>777</v>
+      </c>
+      <c r="E280" s="13" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="16" t="s">
+        <v>779</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C281" s="14" t="s">
+        <v>780</v>
+      </c>
+      <c r="D281" s="12" t="s">
+        <v>781</v>
+      </c>
+      <c r="E281" s="13" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="10" t="s">
+        <v>783</v>
+      </c>
+      <c r="B282" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C282" s="14" t="s">
+        <v>784</v>
+      </c>
+      <c r="D282" s="12" t="s">
+        <v>785</v>
+      </c>
+      <c r="E282" s="13" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="16" t="s">
+        <v>787</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C283" s="14" t="s">
+        <v>788</v>
+      </c>
+      <c r="D283" s="12" t="s">
+        <v>789</v>
+      </c>
+      <c r="E283" s="13" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="16" t="s">
+        <v>791</v>
+      </c>
+      <c r="B284" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C284" s="14" t="s">
+        <v>792</v>
+      </c>
+      <c r="D284" s="12" t="s">
+        <v>793</v>
+      </c>
+      <c r="E284" s="13" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="16" t="s">
+        <v>795</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C285" s="23" t="s">
+        <v>796</v>
+      </c>
+      <c r="D285" s="12" t="s">
+        <v>797</v>
+      </c>
+      <c r="E285" s="13" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C286" s="14" t="s">
+        <v>800</v>
+      </c>
+      <c r="D286" s="12" t="s">
+        <v>801</v>
+      </c>
+      <c r="E286" s="13" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="10" t="s">
+        <v>803</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C287" s="14" t="s">
+        <v>804</v>
+      </c>
+      <c r="D287" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="E287" s="13" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="B288" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C288" s="14" t="s">
+        <v>808</v>
+      </c>
+      <c r="D288" s="12" t="s">
+        <v>809</v>
+      </c>
+      <c r="E288" s="13" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="10" t="s">
+        <v>811</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C289" s="14" t="s">
+        <v>812</v>
+      </c>
+      <c r="D289" s="12" t="s">
+        <v>813</v>
+      </c>
+      <c r="E289" s="13" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="10" t="s">
+        <v>815</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C290" s="19" t="s">
+        <v>816</v>
+      </c>
+      <c r="D290" s="12" t="s">
+        <v>817</v>
+      </c>
+      <c r="E290" s="13" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="22"/>
-      <c r="B291" s="20"/>
-      <c r="C291" s="22"/>
-      <c r="D291" s="22"/>
-      <c r="E291" s="22"/>
+      <c r="A291" s="10" t="s">
+        <v>819</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C291" s="14" t="s">
+        <v>820</v>
+      </c>
+      <c r="D291" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="E291" s="13" t="s">
+        <v>822</v>
+      </c>
     </row>
     <row r="292">
-      <c r="A292" s="22"/>
-      <c r="B292" s="20"/>
-      <c r="C292" s="22"/>
-      <c r="D292" s="22"/>
-      <c r="E292" s="22"/>
+      <c r="A292" s="16" t="s">
+        <v>823</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C292" s="14" t="s">
+        <v>824</v>
+      </c>
+      <c r="D292" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="E292" s="13" t="s">
+        <v>826</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="22"/>
@@ -11730,99 +12863,173 @@
     <hyperlink r:id="rId258" ref="D130"/>
     <hyperlink r:id="rId259" ref="A131"/>
     <hyperlink r:id="rId260" ref="D131"/>
-    <hyperlink r:id="rId261" ref="A166"/>
-    <hyperlink r:id="rId262" ref="D166"/>
-    <hyperlink r:id="rId263" ref="A167"/>
-    <hyperlink r:id="rId264" ref="D167"/>
-    <hyperlink r:id="rId265" ref="A168"/>
-    <hyperlink r:id="rId266" ref="D168"/>
-    <hyperlink r:id="rId267" ref="A169"/>
-    <hyperlink r:id="rId268" ref="D169"/>
-    <hyperlink r:id="rId269" ref="A170"/>
-    <hyperlink r:id="rId270" ref="D170"/>
-    <hyperlink r:id="rId271" ref="A171"/>
-    <hyperlink r:id="rId272" ref="D171"/>
-    <hyperlink r:id="rId273" ref="A172"/>
-    <hyperlink r:id="rId274" ref="D172"/>
-    <hyperlink r:id="rId275" ref="A173"/>
-    <hyperlink r:id="rId276" ref="D173"/>
-    <hyperlink r:id="rId277" ref="A174"/>
-    <hyperlink r:id="rId278" ref="D174"/>
-    <hyperlink r:id="rId279" ref="A175"/>
-    <hyperlink r:id="rId280" ref="D175"/>
-    <hyperlink r:id="rId281" ref="A176"/>
-    <hyperlink r:id="rId282" ref="D176"/>
-    <hyperlink r:id="rId283" ref="A177"/>
-    <hyperlink r:id="rId284" ref="D177"/>
-    <hyperlink r:id="rId285" ref="A178"/>
-    <hyperlink r:id="rId286" ref="D178"/>
-    <hyperlink r:id="rId287" ref="A179"/>
-    <hyperlink r:id="rId288" ref="D179"/>
-    <hyperlink r:id="rId289" ref="A180"/>
-    <hyperlink r:id="rId290" ref="D180"/>
-    <hyperlink r:id="rId291" ref="A181"/>
-    <hyperlink r:id="rId292" ref="D181"/>
-    <hyperlink r:id="rId293" ref="A182"/>
-    <hyperlink r:id="rId294" ref="D182"/>
-    <hyperlink r:id="rId295" ref="A183"/>
-    <hyperlink r:id="rId296" ref="D183"/>
-    <hyperlink r:id="rId297" ref="A184"/>
-    <hyperlink r:id="rId298" ref="D184"/>
-    <hyperlink r:id="rId299" ref="A185"/>
-    <hyperlink r:id="rId300" ref="D185"/>
-    <hyperlink r:id="rId301" ref="A186"/>
-    <hyperlink r:id="rId302" ref="D186"/>
-    <hyperlink r:id="rId303" ref="A187"/>
-    <hyperlink r:id="rId304" ref="D187"/>
-    <hyperlink r:id="rId305" ref="A188"/>
-    <hyperlink r:id="rId306" ref="D188"/>
-    <hyperlink r:id="rId307" ref="A189"/>
-    <hyperlink r:id="rId308" ref="D189"/>
-    <hyperlink r:id="rId309" ref="A190"/>
-    <hyperlink r:id="rId310" ref="D190"/>
-    <hyperlink r:id="rId311" ref="A191"/>
-    <hyperlink r:id="rId312" ref="D191"/>
-    <hyperlink r:id="rId313" ref="A192"/>
-    <hyperlink r:id="rId314" ref="D192"/>
-    <hyperlink r:id="rId315" ref="D200"/>
-    <hyperlink r:id="rId316" ref="D201"/>
-    <hyperlink r:id="rId317" ref="A202"/>
-    <hyperlink r:id="rId318" ref="D202"/>
-    <hyperlink r:id="rId319" ref="A203"/>
-    <hyperlink r:id="rId320" ref="D203"/>
-    <hyperlink r:id="rId321" ref="A204"/>
-    <hyperlink r:id="rId322" ref="D204"/>
-    <hyperlink r:id="rId323" ref="A234"/>
-    <hyperlink r:id="rId324" ref="D234"/>
-    <hyperlink r:id="rId325" ref="A235"/>
-    <hyperlink r:id="rId326" ref="D235"/>
-    <hyperlink r:id="rId327" ref="A236"/>
-    <hyperlink r:id="rId328" ref="D236"/>
-    <hyperlink r:id="rId329" ref="A237"/>
-    <hyperlink r:id="rId330" ref="D237"/>
-    <hyperlink r:id="rId331" ref="A238"/>
-    <hyperlink r:id="rId332" ref="D238"/>
-    <hyperlink r:id="rId333" ref="A239"/>
-    <hyperlink r:id="rId334" ref="D239"/>
-    <hyperlink r:id="rId335" ref="A240"/>
-    <hyperlink r:id="rId336" ref="D240"/>
-    <hyperlink r:id="rId337" ref="A241"/>
-    <hyperlink r:id="rId338" ref="D241"/>
-    <hyperlink r:id="rId339" ref="A242"/>
-    <hyperlink r:id="rId340" ref="D242"/>
-    <hyperlink r:id="rId341" ref="A243"/>
-    <hyperlink r:id="rId342" ref="D243"/>
-    <hyperlink r:id="rId343" ref="A244"/>
-    <hyperlink r:id="rId344" ref="D244"/>
-    <hyperlink r:id="rId345" ref="A245"/>
-    <hyperlink r:id="rId346" ref="D245"/>
-    <hyperlink r:id="rId347" ref="A246"/>
-    <hyperlink r:id="rId348" ref="D246"/>
-    <hyperlink r:id="rId349" ref="A247"/>
-    <hyperlink r:id="rId350" ref="D247"/>
-    <hyperlink r:id="rId351" ref="A248"/>
-    <hyperlink r:id="rId352" ref="D248"/>
+    <hyperlink r:id="rId261" ref="A132"/>
+    <hyperlink r:id="rId262" ref="D132"/>
+    <hyperlink r:id="rId263" ref="A133"/>
+    <hyperlink r:id="rId264" ref="D133"/>
+    <hyperlink r:id="rId265" ref="A134"/>
+    <hyperlink r:id="rId266" ref="D134"/>
+    <hyperlink r:id="rId267" ref="A135"/>
+    <hyperlink r:id="rId268" ref="D135"/>
+    <hyperlink r:id="rId269" ref="A136"/>
+    <hyperlink r:id="rId270" ref="D136"/>
+    <hyperlink r:id="rId271" ref="A137"/>
+    <hyperlink r:id="rId272" ref="D137"/>
+    <hyperlink r:id="rId273" ref="A138"/>
+    <hyperlink r:id="rId274" ref="D138"/>
+    <hyperlink r:id="rId275" ref="A139"/>
+    <hyperlink r:id="rId276" ref="D139"/>
+    <hyperlink r:id="rId277" ref="A140"/>
+    <hyperlink r:id="rId278" ref="D140"/>
+    <hyperlink r:id="rId279" ref="A141"/>
+    <hyperlink r:id="rId280" ref="D141"/>
+    <hyperlink r:id="rId281" ref="A142"/>
+    <hyperlink r:id="rId282" ref="D142"/>
+    <hyperlink r:id="rId283" ref="A143"/>
+    <hyperlink r:id="rId284" ref="D143"/>
+    <hyperlink r:id="rId285" ref="A144"/>
+    <hyperlink r:id="rId286" ref="D144"/>
+    <hyperlink r:id="rId287" ref="A145"/>
+    <hyperlink r:id="rId288" ref="D145"/>
+    <hyperlink r:id="rId289" ref="A146"/>
+    <hyperlink r:id="rId290" ref="D146"/>
+    <hyperlink r:id="rId291" ref="A147"/>
+    <hyperlink r:id="rId292" ref="D147"/>
+    <hyperlink r:id="rId293" ref="A148"/>
+    <hyperlink r:id="rId294" ref="D148"/>
+    <hyperlink r:id="rId295" ref="A149"/>
+    <hyperlink r:id="rId296" ref="D149"/>
+    <hyperlink r:id="rId297" ref="A150"/>
+    <hyperlink r:id="rId298" ref="D150"/>
+    <hyperlink r:id="rId299" ref="A151"/>
+    <hyperlink r:id="rId300" ref="D151"/>
+    <hyperlink r:id="rId301" ref="A152"/>
+    <hyperlink r:id="rId302" ref="D152"/>
+    <hyperlink r:id="rId303" ref="A153"/>
+    <hyperlink r:id="rId304" ref="D153"/>
+    <hyperlink r:id="rId305" ref="A154"/>
+    <hyperlink r:id="rId306" ref="D154"/>
+    <hyperlink r:id="rId307" ref="A155"/>
+    <hyperlink r:id="rId308" ref="D155"/>
+    <hyperlink r:id="rId309" ref="A156"/>
+    <hyperlink r:id="rId310" ref="D156"/>
+    <hyperlink r:id="rId311" ref="A157"/>
+    <hyperlink r:id="rId312" ref="D157"/>
+    <hyperlink r:id="rId313" ref="A158"/>
+    <hyperlink r:id="rId314" ref="D158"/>
+    <hyperlink r:id="rId315" ref="A159"/>
+    <hyperlink r:id="rId316" ref="D159"/>
+    <hyperlink r:id="rId317" ref="A160"/>
+    <hyperlink r:id="rId318" ref="D160"/>
+    <hyperlink r:id="rId319" ref="A161"/>
+    <hyperlink r:id="rId320" ref="D161"/>
+    <hyperlink r:id="rId321" ref="A162"/>
+    <hyperlink r:id="rId322" ref="D162"/>
+    <hyperlink r:id="rId323" ref="A163"/>
+    <hyperlink r:id="rId324" ref="D163"/>
+    <hyperlink r:id="rId325" ref="A164"/>
+    <hyperlink r:id="rId326" ref="D164"/>
+    <hyperlink r:id="rId327" ref="A165"/>
+    <hyperlink r:id="rId328" ref="D165"/>
+    <hyperlink r:id="rId329" ref="A166"/>
+    <hyperlink r:id="rId330" ref="D166"/>
+    <hyperlink r:id="rId331" ref="A167"/>
+    <hyperlink r:id="rId332" ref="D167"/>
+    <hyperlink r:id="rId333" ref="A168"/>
+    <hyperlink r:id="rId334" ref="D168"/>
+    <hyperlink r:id="rId335" ref="A210"/>
+    <hyperlink r:id="rId336" ref="D210"/>
+    <hyperlink r:id="rId337" ref="A211"/>
+    <hyperlink r:id="rId338" ref="D211"/>
+    <hyperlink r:id="rId339" ref="A212"/>
+    <hyperlink r:id="rId340" ref="D212"/>
+    <hyperlink r:id="rId341" ref="A213"/>
+    <hyperlink r:id="rId342" ref="D213"/>
+    <hyperlink r:id="rId343" ref="A214"/>
+    <hyperlink r:id="rId344" ref="D214"/>
+    <hyperlink r:id="rId345" ref="A215"/>
+    <hyperlink r:id="rId346" ref="D215"/>
+    <hyperlink r:id="rId347" ref="A216"/>
+    <hyperlink r:id="rId348" ref="D216"/>
+    <hyperlink r:id="rId349" ref="A217"/>
+    <hyperlink r:id="rId350" ref="D217"/>
+    <hyperlink r:id="rId351" ref="A218"/>
+    <hyperlink r:id="rId352" ref="D218"/>
+    <hyperlink r:id="rId353" ref="A219"/>
+    <hyperlink r:id="rId354" ref="D219"/>
+    <hyperlink r:id="rId355" ref="A220"/>
+    <hyperlink r:id="rId356" ref="D220"/>
+    <hyperlink r:id="rId357" ref="A221"/>
+    <hyperlink r:id="rId358" ref="D221"/>
+    <hyperlink r:id="rId359" ref="A222"/>
+    <hyperlink r:id="rId360" ref="D222"/>
+    <hyperlink r:id="rId361" ref="A223"/>
+    <hyperlink r:id="rId362" ref="D223"/>
+    <hyperlink r:id="rId363" ref="A224"/>
+    <hyperlink r:id="rId364" ref="D224"/>
+    <hyperlink r:id="rId365" ref="A225"/>
+    <hyperlink r:id="rId366" ref="D225"/>
+    <hyperlink r:id="rId367" ref="A226"/>
+    <hyperlink r:id="rId368" ref="D226"/>
+    <hyperlink r:id="rId369" ref="A227"/>
+    <hyperlink r:id="rId370" ref="D227"/>
+    <hyperlink r:id="rId371" ref="A228"/>
+    <hyperlink r:id="rId372" ref="D228"/>
+    <hyperlink r:id="rId373" ref="A229"/>
+    <hyperlink r:id="rId374" ref="D229"/>
+    <hyperlink r:id="rId375" ref="A230"/>
+    <hyperlink r:id="rId376" ref="D230"/>
+    <hyperlink r:id="rId377" ref="A231"/>
+    <hyperlink r:id="rId378" ref="D231"/>
+    <hyperlink r:id="rId379" ref="A232"/>
+    <hyperlink r:id="rId380" ref="D232"/>
+    <hyperlink r:id="rId381" ref="A233"/>
+    <hyperlink r:id="rId382" ref="D233"/>
+    <hyperlink r:id="rId383" ref="A234"/>
+    <hyperlink r:id="rId384" ref="D234"/>
+    <hyperlink r:id="rId385" ref="A235"/>
+    <hyperlink r:id="rId386" ref="D235"/>
+    <hyperlink r:id="rId387" ref="A236"/>
+    <hyperlink r:id="rId388" ref="D236"/>
+    <hyperlink r:id="rId389" ref="D244"/>
+    <hyperlink r:id="rId390" ref="D245"/>
+    <hyperlink r:id="rId391" ref="A246"/>
+    <hyperlink r:id="rId392" ref="D246"/>
+    <hyperlink r:id="rId393" ref="A247"/>
+    <hyperlink r:id="rId394" ref="D247"/>
+    <hyperlink r:id="rId395" ref="A248"/>
+    <hyperlink r:id="rId396" ref="D248"/>
+    <hyperlink r:id="rId397" ref="A278"/>
+    <hyperlink r:id="rId398" ref="D278"/>
+    <hyperlink r:id="rId399" ref="A279"/>
+    <hyperlink r:id="rId400" ref="D279"/>
+    <hyperlink r:id="rId401" ref="A280"/>
+    <hyperlink r:id="rId402" ref="D280"/>
+    <hyperlink r:id="rId403" ref="A281"/>
+    <hyperlink r:id="rId404" ref="D281"/>
+    <hyperlink r:id="rId405" ref="A282"/>
+    <hyperlink r:id="rId406" ref="D282"/>
+    <hyperlink r:id="rId407" ref="A283"/>
+    <hyperlink r:id="rId408" ref="D283"/>
+    <hyperlink r:id="rId409" ref="A284"/>
+    <hyperlink r:id="rId410" ref="D284"/>
+    <hyperlink r:id="rId411" ref="A285"/>
+    <hyperlink r:id="rId412" ref="D285"/>
+    <hyperlink r:id="rId413" ref="A286"/>
+    <hyperlink r:id="rId414" ref="D286"/>
+    <hyperlink r:id="rId415" ref="A287"/>
+    <hyperlink r:id="rId416" ref="D287"/>
+    <hyperlink r:id="rId417" ref="A288"/>
+    <hyperlink r:id="rId418" ref="D288"/>
+    <hyperlink r:id="rId419" ref="A289"/>
+    <hyperlink r:id="rId420" ref="D289"/>
+    <hyperlink r:id="rId421" ref="A290"/>
+    <hyperlink r:id="rId422" ref="D290"/>
+    <hyperlink r:id="rId423" ref="A291"/>
+    <hyperlink r:id="rId424" ref="D291"/>
+    <hyperlink r:id="rId425" ref="A292"/>
+    <hyperlink r:id="rId426" ref="D292"/>
   </hyperlinks>
-  <drawing r:id="rId353"/>
+  <drawing r:id="rId427"/>
 </worksheet>
 </file>